--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>23</v>
-      </c>
       <c r="D7" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F11" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="J11" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>76</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.02631578947368421</v>
+        <v>2</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -824,13 +824,13 @@
         <v>45</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>33</v>
@@ -842,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,19 +821,19 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>15</v>
@@ -842,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,19 +821,19 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>15</v>
@@ -842,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -824,13 +824,13 @@
         <v>48</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>36</v>
@@ -842,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N11" headerRowCount="1">
-  <autoFilter ref="A10:N11"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O11" headerRowCount="1">
+  <autoFilter ref="A10:O11"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -845,13 +845,13 @@
         <v>48</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>36</v>
@@ -863,7 +863,7 @@
         <v>12</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>96</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>91</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -845,13 +845,13 @@
         <v>54</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>41</v>
@@ -863,7 +863,7 @@
         <v>13</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>114</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>57</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H11" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>22</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR TEMPESTA ALESSIO.xlsx
@@ -687,7 +687,7 @@
         <v>66</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>23</v>
@@ -854,7 +854,7 @@
         <v>60</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>22</v>
@@ -863,7 +863,7 @@
         <v>14</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>2</v>
